--- a/backend/data/financials_by_company/0FO.F.xlsx
+++ b/backend/data/financials_by_company/0FO.F.xlsx
@@ -642,506 +642,506 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45535</v>
+        <v>44439</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.193</v>
       </c>
       <c r="D2" t="n">
-        <v>16769000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>45922000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1000</v>
+      </c>
       <c r="G2" t="n">
-        <v>2608000</v>
+        <v>28279000</v>
       </c>
       <c r="H2" t="n">
-        <v>14085000</v>
+        <v>10148000</v>
       </c>
       <c r="I2" t="n">
-        <v>88031000</v>
+        <v>89805000</v>
       </c>
       <c r="J2" t="n">
-        <v>16769000</v>
+        <v>45922000</v>
       </c>
       <c r="K2" t="n">
-        <v>2684000</v>
+        <v>35774000</v>
       </c>
       <c r="L2" t="n">
-        <v>-2951000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>180000</v>
-      </c>
+        <v>-403000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2608000</v>
+        <v>28279000</v>
       </c>
       <c r="P2" t="n">
-        <v>2608000</v>
+        <v>28279000</v>
       </c>
       <c r="Q2" t="n">
-        <v>152828000</v>
+        <v>138161000</v>
       </c>
       <c r="R2" t="n">
-        <v>5696000</v>
+        <v>35774000</v>
       </c>
       <c r="S2" t="n">
-        <v>59400000</v>
+        <v>58718000</v>
       </c>
       <c r="T2" t="n">
-        <v>58612000</v>
+        <v>57993000</v>
       </c>
       <c r="U2" t="n">
-        <v>0.044</v>
+        <v>0.482</v>
       </c>
       <c r="V2" t="n">
-        <v>0.045</v>
+        <v>0.488</v>
       </c>
       <c r="W2" t="n">
-        <v>2608000</v>
+        <v>28279000</v>
       </c>
       <c r="X2" t="n">
-        <v>2608000</v>
+        <v>28279000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>2608000</v>
+        <v>28279000</v>
       </c>
       <c r="AA2" t="n">
-        <v>2608000</v>
+        <v>28279000</v>
       </c>
       <c r="AB2" t="n">
-        <v>2608000</v>
+        <v>28279000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-104000</v>
+        <v>6759000</v>
       </c>
       <c r="AD2" t="n">
-        <v>2504000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+        <v>35038000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>-2951000</v>
+        <v>-403000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2871000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>180000</v>
-      </c>
+        <v>403000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>5696000</v>
+        <v>35774000</v>
       </c>
       <c r="AL2" t="n">
-        <v>64797000</v>
+        <v>48356000</v>
       </c>
       <c r="AM2" t="n">
-        <v>64797000</v>
+        <v>48356000</v>
       </c>
       <c r="AN2" t="n">
-        <v>64797000</v>
+        <v>48356000</v>
       </c>
       <c r="AO2" t="n">
-        <v>70493000</v>
+        <v>84130000</v>
       </c>
       <c r="AP2" t="n">
-        <v>88031000</v>
+        <v>89805000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>158524000</v>
+        <v>173935000</v>
       </c>
       <c r="AR2" t="n">
-        <v>158524000</v>
+        <v>173935000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45169</v>
+        <v>44804</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.218</v>
+        <v>0.189</v>
       </c>
       <c r="D3" t="n">
-        <v>35439000</v>
+        <v>40767000</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>17797000</v>
+        <v>24776000</v>
       </c>
       <c r="H3" t="n">
-        <v>12538000</v>
+        <v>12106000</v>
       </c>
       <c r="I3" t="n">
-        <v>93616000</v>
+        <v>100453000</v>
       </c>
       <c r="J3" t="n">
-        <v>35439000</v>
+        <v>40767000</v>
       </c>
       <c r="K3" t="n">
-        <v>22901000</v>
+        <v>28661000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1926000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>153000</v>
-      </c>
+        <v>-476000</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>132000</v>
+        <v>11000</v>
       </c>
       <c r="O3" t="n">
-        <v>17797000</v>
+        <v>24776000</v>
       </c>
       <c r="P3" t="n">
-        <v>17797000</v>
+        <v>24776000</v>
       </c>
       <c r="Q3" t="n">
-        <v>154122000</v>
+        <v>155072000</v>
       </c>
       <c r="R3" t="n">
-        <v>24343000</v>
+        <v>28661000</v>
       </c>
       <c r="S3" t="n">
-        <v>58953000</v>
+        <v>58917000</v>
       </c>
       <c r="T3" t="n">
-        <v>58506000</v>
+        <v>58294000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.302</v>
+        <v>0.421</v>
       </c>
       <c r="V3" t="n">
-        <v>0.304</v>
+        <v>0.425</v>
       </c>
       <c r="W3" t="n">
-        <v>17797000</v>
+        <v>24776000</v>
       </c>
       <c r="X3" t="n">
-        <v>17797000</v>
+        <v>24776000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17797000</v>
+        <v>24776000</v>
       </c>
       <c r="AA3" t="n">
-        <v>17797000</v>
+        <v>24776000</v>
       </c>
       <c r="AB3" t="n">
-        <v>17797000</v>
+        <v>24776000</v>
       </c>
       <c r="AC3" t="n">
-        <v>4951000</v>
+        <v>5773000</v>
       </c>
       <c r="AD3" t="n">
-        <v>22748000</v>
+        <v>30549000</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>-1926000</v>
+        <v>-476000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1905000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>153000</v>
-      </c>
+        <v>487000</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>132000</v>
+        <v>11000</v>
       </c>
       <c r="AK3" t="n">
-        <v>24343000</v>
+        <v>28661000</v>
       </c>
       <c r="AL3" t="n">
-        <v>60506000</v>
+        <v>54619000</v>
       </c>
       <c r="AM3" t="n">
-        <v>60506000</v>
+        <v>54619000</v>
       </c>
       <c r="AN3" t="n">
-        <v>60506000</v>
+        <v>54619000</v>
       </c>
       <c r="AO3" t="n">
-        <v>84849000</v>
+        <v>83280000</v>
       </c>
       <c r="AP3" t="n">
-        <v>93616000</v>
+        <v>100453000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>178465000</v>
+        <v>183733000</v>
       </c>
       <c r="AR3" t="n">
-        <v>178465000</v>
+        <v>183733000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44804</v>
+        <v>45169</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.189</v>
+        <v>0.218</v>
       </c>
       <c r="D4" t="n">
-        <v>40767000</v>
+        <v>35439000</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>24776000</v>
+        <v>17797000</v>
       </c>
       <c r="H4" t="n">
-        <v>12106000</v>
+        <v>12538000</v>
       </c>
       <c r="I4" t="n">
-        <v>100453000</v>
+        <v>93616000</v>
       </c>
       <c r="J4" t="n">
-        <v>40767000</v>
+        <v>35439000</v>
       </c>
       <c r="K4" t="n">
-        <v>28661000</v>
+        <v>22901000</v>
       </c>
       <c r="L4" t="n">
-        <v>-476000</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>-1926000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>153000</v>
+      </c>
       <c r="N4" t="n">
-        <v>11000</v>
+        <v>132000</v>
       </c>
       <c r="O4" t="n">
-        <v>24776000</v>
+        <v>17797000</v>
       </c>
       <c r="P4" t="n">
-        <v>24776000</v>
+        <v>17797000</v>
       </c>
       <c r="Q4" t="n">
-        <v>155072000</v>
+        <v>154122000</v>
       </c>
       <c r="R4" t="n">
-        <v>28661000</v>
+        <v>24343000</v>
       </c>
       <c r="S4" t="n">
-        <v>58917000</v>
+        <v>58953000</v>
       </c>
       <c r="T4" t="n">
-        <v>58294000</v>
+        <v>58506000</v>
       </c>
       <c r="U4" t="n">
-        <v>0.421</v>
+        <v>0.302</v>
       </c>
       <c r="V4" t="n">
-        <v>0.425</v>
+        <v>0.304</v>
       </c>
       <c r="W4" t="n">
-        <v>24776000</v>
+        <v>17797000</v>
       </c>
       <c r="X4" t="n">
-        <v>24776000</v>
+        <v>17797000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>24776000</v>
+        <v>17797000</v>
       </c>
       <c r="AA4" t="n">
-        <v>24776000</v>
+        <v>17797000</v>
       </c>
       <c r="AB4" t="n">
-        <v>24776000</v>
+        <v>17797000</v>
       </c>
       <c r="AC4" t="n">
-        <v>5773000</v>
+        <v>4951000</v>
       </c>
       <c r="AD4" t="n">
-        <v>30549000</v>
+        <v>22748000</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>-476000</v>
+        <v>-1926000</v>
       </c>
       <c r="AH4" t="n">
-        <v>487000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>1905000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>153000</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>11000</v>
+        <v>132000</v>
       </c>
       <c r="AK4" t="n">
-        <v>28661000</v>
+        <v>24343000</v>
       </c>
       <c r="AL4" t="n">
-        <v>54619000</v>
+        <v>60506000</v>
       </c>
       <c r="AM4" t="n">
-        <v>54619000</v>
+        <v>60506000</v>
       </c>
       <c r="AN4" t="n">
-        <v>54619000</v>
+        <v>60506000</v>
       </c>
       <c r="AO4" t="n">
-        <v>83280000</v>
+        <v>84849000</v>
       </c>
       <c r="AP4" t="n">
-        <v>100453000</v>
+        <v>93616000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>183733000</v>
+        <v>178465000</v>
       </c>
       <c r="AR4" t="n">
-        <v>183733000</v>
+        <v>178465000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44439</v>
+        <v>45535</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.193</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>45922000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-1000</v>
-      </c>
+        <v>16769000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>28279000</v>
+        <v>2608000</v>
       </c>
       <c r="H5" t="n">
-        <v>10148000</v>
+        <v>14085000</v>
       </c>
       <c r="I5" t="n">
-        <v>89805000</v>
+        <v>88031000</v>
       </c>
       <c r="J5" t="n">
-        <v>45922000</v>
+        <v>16769000</v>
       </c>
       <c r="K5" t="n">
-        <v>35774000</v>
+        <v>2684000</v>
       </c>
       <c r="L5" t="n">
-        <v>-403000</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>-2951000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>180000</v>
+      </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="O5" t="n">
-        <v>28279000</v>
+        <v>2608000</v>
       </c>
       <c r="P5" t="n">
-        <v>28279000</v>
+        <v>2608000</v>
       </c>
       <c r="Q5" t="n">
-        <v>138161000</v>
+        <v>152828000</v>
       </c>
       <c r="R5" t="n">
-        <v>35774000</v>
+        <v>5696000</v>
       </c>
       <c r="S5" t="n">
-        <v>58718000</v>
+        <v>59400000</v>
       </c>
       <c r="T5" t="n">
-        <v>57993000</v>
+        <v>58612000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.482</v>
+        <v>0.044</v>
       </c>
       <c r="V5" t="n">
-        <v>0.488</v>
+        <v>0.045</v>
       </c>
       <c r="W5" t="n">
-        <v>28279000</v>
+        <v>2608000</v>
       </c>
       <c r="X5" t="n">
-        <v>28279000</v>
+        <v>2608000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>28279000</v>
+        <v>2608000</v>
       </c>
       <c r="AA5" t="n">
-        <v>28279000</v>
+        <v>2608000</v>
       </c>
       <c r="AB5" t="n">
-        <v>28279000</v>
+        <v>2608000</v>
       </c>
       <c r="AC5" t="n">
-        <v>6759000</v>
+        <v>-104000</v>
       </c>
       <c r="AD5" t="n">
-        <v>35038000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
+        <v>2504000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>-403000</v>
+        <v>-2951000</v>
       </c>
       <c r="AH5" t="n">
-        <v>403000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>2871000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>180000</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="AK5" t="n">
-        <v>35774000</v>
+        <v>5696000</v>
       </c>
       <c r="AL5" t="n">
-        <v>48356000</v>
+        <v>64797000</v>
       </c>
       <c r="AM5" t="n">
-        <v>48356000</v>
+        <v>64797000</v>
       </c>
       <c r="AN5" t="n">
-        <v>48356000</v>
+        <v>64797000</v>
       </c>
       <c r="AO5" t="n">
-        <v>84130000</v>
+        <v>70493000</v>
       </c>
       <c r="AP5" t="n">
-        <v>89805000</v>
+        <v>88031000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>173935000</v>
+        <v>158524000</v>
       </c>
       <c r="AR5" t="n">
-        <v>173935000</v>
+        <v>158524000</v>
       </c>
     </row>
   </sheetData>
@@ -1487,54 +1487,54 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45535</v>
-      </c>
-      <c r="B2" t="n">
-        <v>588017</v>
-      </c>
+        <v>44439</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>58623622</v>
+        <v>58661639</v>
       </c>
       <c r="D2" t="n">
-        <v>59211639</v>
-      </c>
-      <c r="E2" t="n">
-        <v>12525000</v>
-      </c>
+        <v>58661639</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>42885000</v>
+        <v>1040000</v>
       </c>
       <c r="G2" t="n">
-        <v>35697000</v>
+        <v>25227000</v>
       </c>
       <c r="H2" t="n">
-        <v>150521000</v>
+        <v>84099000</v>
       </c>
       <c r="I2" t="n">
-        <v>39543000</v>
+        <v>28909000</v>
       </c>
       <c r="J2" t="n">
-        <v>35697000</v>
+        <v>25227000</v>
       </c>
       <c r="K2" t="n">
-        <v>8320000</v>
+        <v>1288000</v>
       </c>
       <c r="L2" t="n">
-        <v>115956000</v>
+        <v>84347000</v>
       </c>
       <c r="M2" t="n">
-        <v>115956000</v>
+        <v>84099000</v>
       </c>
       <c r="N2" t="n">
-        <v>115956000</v>
+        <v>84347000</v>
       </c>
       <c r="O2" t="n">
-        <v>115956000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+        <v>84347000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1000</v>
+      </c>
       <c r="R2" t="n">
-        <v>118015000</v>
+        <v>82539000</v>
       </c>
       <c r="S2" t="n">
         <v>115000</v>
@@ -1546,176 +1546,184 @@
         <v>59000</v>
       </c>
       <c r="V2" t="n">
-        <v>86989000</v>
+        <v>32867000</v>
       </c>
       <c r="W2" t="n">
-        <v>17608000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>7328000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
       <c r="Y2" t="n">
-        <v>10815000</v>
+        <v>5996000</v>
       </c>
       <c r="Z2" t="n">
-        <v>6793000</v>
+        <v>262000</v>
       </c>
       <c r="AA2" t="n">
-        <v>6793000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+        <v>510000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-248000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1069000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>69381000</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>25539000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-4000</v>
+      </c>
       <c r="AF2" t="n">
-        <v>36092000</v>
+        <v>778000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1527000</v>
+        <v>778000</v>
       </c>
       <c r="AH2" t="n">
-        <v>34565000</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>522000</v>
+        <v>1092000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22228000</v>
+        <v>11969000</v>
       </c>
       <c r="AK2" t="n">
-        <v>3518000</v>
+        <v>449000</v>
       </c>
       <c r="AL2" t="n">
-        <v>18710000</v>
+        <v>11520000</v>
       </c>
       <c r="AM2" t="n">
-        <v>202945000</v>
+        <v>117214000</v>
       </c>
       <c r="AN2" t="n">
-        <v>94021000</v>
+        <v>62766000</v>
       </c>
       <c r="AO2" t="n">
-        <v>2666000</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>80259000</v>
+        <v>59120000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>66065000</v>
+        <v>49066000</v>
       </c>
       <c r="AR2" t="n">
-        <v>14194000</v>
+        <v>10054000</v>
       </c>
       <c r="AS2" t="n">
-        <v>11096000</v>
+        <v>3646000</v>
       </c>
       <c r="AT2" t="n">
-        <v>-13811000</v>
+        <v>-6496000</v>
       </c>
       <c r="AU2" t="n">
-        <v>24907000</v>
+        <v>10142000</v>
       </c>
       <c r="AV2" t="n">
-        <v>11963000</v>
+        <v>3468000</v>
       </c>
       <c r="AW2" t="n">
-        <v>11444000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+        <v>6674000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
       <c r="AY2" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>108924000</v>
+        <v>54448000</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>716000</v>
       </c>
       <c r="BB2" t="n">
-        <v>2943000</v>
+        <v>1484000</v>
       </c>
       <c r="BC2" t="n">
-        <v>49267000</v>
+        <v>20749000</v>
       </c>
       <c r="BD2" t="n">
-        <v>42543000</v>
+        <v>17052000</v>
       </c>
       <c r="BE2" t="n">
-        <v>1986000</v>
+        <v>1471000</v>
       </c>
       <c r="BF2" t="n">
-        <v>4738000</v>
+        <v>2226000</v>
       </c>
       <c r="BG2" t="n">
-        <v>470000</v>
+        <v>1042000</v>
       </c>
       <c r="BH2" t="n">
-        <v>750000</v>
+        <v>1368000</v>
       </c>
       <c r="BI2" t="n">
-        <v>33454000</v>
+        <v>11750000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-254000</v>
+        <v>-484000</v>
       </c>
       <c r="BK2" t="n">
-        <v>33708000</v>
+        <v>12234000</v>
       </c>
       <c r="BL2" t="n">
-        <v>22040000</v>
+        <v>17339000</v>
       </c>
       <c r="BM2" t="n">
-        <v>22040000</v>
+        <v>17339000</v>
       </c>
       <c r="BN2" t="n">
-        <v>22040000</v>
+        <v>17339000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45169</v>
-      </c>
-      <c r="B3" t="n">
-        <v>624173</v>
-      </c>
+        <v>44804</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>58587466</v>
+        <v>58661639</v>
       </c>
       <c r="D3" t="n">
-        <v>59211639</v>
+        <v>58661639</v>
       </c>
       <c r="E3" t="n">
-        <v>1306000</v>
+        <v>296000</v>
       </c>
       <c r="F3" t="n">
-        <v>37925000</v>
+        <v>23538000</v>
       </c>
       <c r="G3" t="n">
-        <v>35605000</v>
+        <v>29624000</v>
       </c>
       <c r="H3" t="n">
-        <v>146545000</v>
+        <v>118370000</v>
       </c>
       <c r="I3" t="n">
-        <v>41472000</v>
+        <v>35789000</v>
       </c>
       <c r="J3" t="n">
-        <v>35605000</v>
+        <v>29624000</v>
       </c>
       <c r="K3" t="n">
-        <v>9832000</v>
+        <v>10484000</v>
       </c>
       <c r="L3" t="n">
-        <v>118452000</v>
+        <v>105316000</v>
       </c>
       <c r="M3" t="n">
-        <v>118452000</v>
+        <v>105316000</v>
       </c>
       <c r="N3" t="n">
-        <v>118452000</v>
+        <v>105316000</v>
       </c>
       <c r="O3" t="n">
-        <v>118452000</v>
+        <v>105316000</v>
       </c>
       <c r="P3" t="n">
         <v>-1000</v>
@@ -1724,7 +1732,7 @@
         <v>1000</v>
       </c>
       <c r="R3" t="n">
-        <v>119097000</v>
+        <v>105003000</v>
       </c>
       <c r="S3" t="n">
         <v>115000</v>
@@ -1736,174 +1744,180 @@
         <v>59000</v>
       </c>
       <c r="V3" t="n">
-        <v>92341000</v>
+        <v>72215000</v>
       </c>
       <c r="W3" t="n">
-        <v>18895000</v>
+        <v>17973000</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>10824000</v>
+        <v>9130000</v>
       </c>
       <c r="Z3" t="n">
-        <v>8071000</v>
+        <v>8843000</v>
       </c>
       <c r="AA3" t="n">
-        <v>8071000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>8843000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>73446000</v>
+        <v>54242000</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>29854000</v>
+        <v>14695000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1761000</v>
+        <v>1641000</v>
       </c>
       <c r="AH3" t="n">
-        <v>28093000</v>
+        <v>13054000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1270000</v>
+        <v>1840000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29867000</v>
+        <v>24863000</v>
       </c>
       <c r="AK3" t="n">
-        <v>3823000</v>
+        <v>2054000</v>
       </c>
       <c r="AL3" t="n">
-        <v>26044000</v>
+        <v>22809000</v>
       </c>
       <c r="AM3" t="n">
-        <v>210793000</v>
+        <v>177531000</v>
       </c>
       <c r="AN3" t="n">
-        <v>95875000</v>
+        <v>87500000</v>
       </c>
       <c r="AO3" t="n">
-        <v>533000</v>
+        <v>938000</v>
       </c>
       <c r="AP3" t="n">
-        <v>82847000</v>
+        <v>75692000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>66709000</v>
+        <v>61964000</v>
       </c>
       <c r="AR3" t="n">
-        <v>16138000</v>
+        <v>13728000</v>
       </c>
       <c r="AS3" t="n">
-        <v>12495000</v>
+        <v>10870000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-11039000</v>
+        <v>-8705000</v>
       </c>
       <c r="AU3" t="n">
-        <v>23534000</v>
+        <v>19575000</v>
       </c>
       <c r="AV3" t="n">
-        <v>11250000</v>
+        <v>10391000</v>
       </c>
       <c r="AW3" t="n">
-        <v>10784000</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>7684000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1500000</v>
+      </c>
       <c r="AY3" t="n">
         <v>1500000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>114918000</v>
+        <v>90031000</v>
       </c>
       <c r="BA3" t="n">
-        <v>491000</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>2370000</v>
+        <v>1285000</v>
       </c>
       <c r="BC3" t="n">
-        <v>55256000</v>
+        <v>48340000</v>
       </c>
       <c r="BD3" t="n">
-        <v>43795000</v>
+        <v>41742000</v>
       </c>
       <c r="BE3" t="n">
-        <v>2011000</v>
+        <v>2778000</v>
       </c>
       <c r="BF3" t="n">
-        <v>9450000</v>
+        <v>3820000</v>
       </c>
       <c r="BG3" t="n">
-        <v>362000</v>
+        <v>127000</v>
       </c>
       <c r="BH3" t="n">
-        <v>1035000</v>
+        <v>634000</v>
       </c>
       <c r="BI3" t="n">
-        <v>28617000</v>
+        <v>26887000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-166000</v>
+        <v>-458000</v>
       </c>
       <c r="BK3" t="n">
-        <v>28783000</v>
+        <v>27345000</v>
       </c>
       <c r="BL3" t="n">
-        <v>26787000</v>
+        <v>12758000</v>
       </c>
       <c r="BM3" t="n">
-        <v>26787000</v>
+        <v>12758000</v>
       </c>
       <c r="BN3" t="n">
-        <v>26787000</v>
+        <v>12758000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44804</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45169</v>
+      </c>
+      <c r="B4" t="n">
+        <v>624173</v>
+      </c>
       <c r="C4" t="n">
-        <v>58661639</v>
+        <v>58587466</v>
       </c>
       <c r="D4" t="n">
-        <v>58661639</v>
+        <v>59211639</v>
       </c>
       <c r="E4" t="n">
-        <v>296000</v>
+        <v>1306000</v>
       </c>
       <c r="F4" t="n">
-        <v>23538000</v>
+        <v>37925000</v>
       </c>
       <c r="G4" t="n">
-        <v>29624000</v>
+        <v>35605000</v>
       </c>
       <c r="H4" t="n">
-        <v>118370000</v>
+        <v>146545000</v>
       </c>
       <c r="I4" t="n">
-        <v>35789000</v>
+        <v>41472000</v>
       </c>
       <c r="J4" t="n">
-        <v>29624000</v>
+        <v>35605000</v>
       </c>
       <c r="K4" t="n">
-        <v>10484000</v>
+        <v>9832000</v>
       </c>
       <c r="L4" t="n">
-        <v>105316000</v>
+        <v>118452000</v>
       </c>
       <c r="M4" t="n">
-        <v>105316000</v>
+        <v>118452000</v>
       </c>
       <c r="N4" t="n">
-        <v>105316000</v>
+        <v>118452000</v>
       </c>
       <c r="O4" t="n">
-        <v>105316000</v>
+        <v>118452000</v>
       </c>
       <c r="P4" t="n">
         <v>-1000</v>
@@ -1912,7 +1926,7 @@
         <v>1000</v>
       </c>
       <c r="R4" t="n">
-        <v>105003000</v>
+        <v>119097000</v>
       </c>
       <c r="S4" t="n">
         <v>115000</v>
@@ -1924,185 +1938,181 @@
         <v>59000</v>
       </c>
       <c r="V4" t="n">
-        <v>72215000</v>
+        <v>92341000</v>
       </c>
       <c r="W4" t="n">
-        <v>17973000</v>
+        <v>18895000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>9130000</v>
+        <v>10824000</v>
       </c>
       <c r="Z4" t="n">
-        <v>8843000</v>
+        <v>8071000</v>
       </c>
       <c r="AA4" t="n">
-        <v>8843000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>8071000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>54242000</v>
+        <v>73446000</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>14695000</v>
+        <v>29854000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1641000</v>
+        <v>1761000</v>
       </c>
       <c r="AH4" t="n">
-        <v>13054000</v>
+        <v>28093000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1840000</v>
+        <v>1270000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24863000</v>
+        <v>29867000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2054000</v>
+        <v>3823000</v>
       </c>
       <c r="AL4" t="n">
-        <v>22809000</v>
+        <v>26044000</v>
       </c>
       <c r="AM4" t="n">
-        <v>177531000</v>
+        <v>210793000</v>
       </c>
       <c r="AN4" t="n">
-        <v>87500000</v>
+        <v>95875000</v>
       </c>
       <c r="AO4" t="n">
-        <v>938000</v>
+        <v>533000</v>
       </c>
       <c r="AP4" t="n">
-        <v>75692000</v>
+        <v>82847000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>61964000</v>
+        <v>66709000</v>
       </c>
       <c r="AR4" t="n">
-        <v>13728000</v>
+        <v>16138000</v>
       </c>
       <c r="AS4" t="n">
-        <v>10870000</v>
+        <v>12495000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-8705000</v>
+        <v>-11039000</v>
       </c>
       <c r="AU4" t="n">
-        <v>19575000</v>
+        <v>23534000</v>
       </c>
       <c r="AV4" t="n">
-        <v>10391000</v>
+        <v>11250000</v>
       </c>
       <c r="AW4" t="n">
-        <v>7684000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1500000</v>
-      </c>
+        <v>10784000</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
         <v>1500000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>90031000</v>
+        <v>114918000</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>491000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1285000</v>
+        <v>2370000</v>
       </c>
       <c r="BC4" t="n">
-        <v>48340000</v>
+        <v>55256000</v>
       </c>
       <c r="BD4" t="n">
-        <v>41742000</v>
+        <v>43795000</v>
       </c>
       <c r="BE4" t="n">
-        <v>2778000</v>
+        <v>2011000</v>
       </c>
       <c r="BF4" t="n">
-        <v>3820000</v>
+        <v>9450000</v>
       </c>
       <c r="BG4" t="n">
-        <v>127000</v>
+        <v>362000</v>
       </c>
       <c r="BH4" t="n">
-        <v>634000</v>
+        <v>1035000</v>
       </c>
       <c r="BI4" t="n">
-        <v>26887000</v>
+        <v>28617000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-458000</v>
+        <v>-166000</v>
       </c>
       <c r="BK4" t="n">
-        <v>27345000</v>
+        <v>28783000</v>
       </c>
       <c r="BL4" t="n">
-        <v>12758000</v>
+        <v>26787000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12758000</v>
+        <v>26787000</v>
       </c>
       <c r="BN4" t="n">
-        <v>12758000</v>
+        <v>26787000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44439</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45535</v>
+      </c>
+      <c r="B5" t="n">
+        <v>588017</v>
+      </c>
       <c r="C5" t="n">
-        <v>58661639</v>
+        <v>58623622</v>
       </c>
       <c r="D5" t="n">
-        <v>58661639</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>59211639</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12525000</v>
+      </c>
       <c r="F5" t="n">
-        <v>1040000</v>
+        <v>42885000</v>
       </c>
       <c r="G5" t="n">
-        <v>25227000</v>
+        <v>35697000</v>
       </c>
       <c r="H5" t="n">
-        <v>84099000</v>
+        <v>150521000</v>
       </c>
       <c r="I5" t="n">
-        <v>28909000</v>
+        <v>39543000</v>
       </c>
       <c r="J5" t="n">
-        <v>25227000</v>
+        <v>35697000</v>
       </c>
       <c r="K5" t="n">
-        <v>1288000</v>
+        <v>8320000</v>
       </c>
       <c r="L5" t="n">
-        <v>84347000</v>
+        <v>115956000</v>
       </c>
       <c r="M5" t="n">
-        <v>84099000</v>
+        <v>115956000</v>
       </c>
       <c r="N5" t="n">
-        <v>84347000</v>
+        <v>115956000</v>
       </c>
       <c r="O5" t="n">
-        <v>84347000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1000</v>
-      </c>
+        <v>115956000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>82539000</v>
+        <v>118015000</v>
       </c>
       <c r="S5" t="n">
         <v>115000</v>
@@ -2114,139 +2124,129 @@
         <v>59000</v>
       </c>
       <c r="V5" t="n">
-        <v>32867000</v>
+        <v>86989000</v>
       </c>
       <c r="W5" t="n">
-        <v>7328000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
+        <v>17608000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>5996000</v>
+        <v>10815000</v>
       </c>
       <c r="Z5" t="n">
-        <v>262000</v>
+        <v>6793000</v>
       </c>
       <c r="AA5" t="n">
-        <v>510000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-248000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1069000</v>
-      </c>
+        <v>6793000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>25539000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-4000</v>
-      </c>
+        <v>69381000</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>778000</v>
+        <v>36092000</v>
       </c>
       <c r="AG5" t="n">
-        <v>778000</v>
+        <v>1527000</v>
       </c>
       <c r="AH5" t="n">
+        <v>34565000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>522000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>22228000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>3518000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>18710000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>202945000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>94021000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2666000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>80259000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>66065000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>14194000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>11096000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-13811000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>24907000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>11963000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>11444000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>108924000</v>
+      </c>
+      <c r="BA5" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" t="n">
-        <v>1092000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>11969000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>449000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>11520000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>117214000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>62766000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>59120000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>49066000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10054000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>3646000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-6496000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>10142000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3468000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>6674000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>54448000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>716000</v>
-      </c>
       <c r="BB5" t="n">
-        <v>1484000</v>
+        <v>2943000</v>
       </c>
       <c r="BC5" t="n">
-        <v>20749000</v>
+        <v>49267000</v>
       </c>
       <c r="BD5" t="n">
-        <v>17052000</v>
+        <v>42543000</v>
       </c>
       <c r="BE5" t="n">
-        <v>1471000</v>
+        <v>1986000</v>
       </c>
       <c r="BF5" t="n">
-        <v>2226000</v>
+        <v>4738000</v>
       </c>
       <c r="BG5" t="n">
-        <v>1042000</v>
+        <v>470000</v>
       </c>
       <c r="BH5" t="n">
-        <v>1368000</v>
+        <v>750000</v>
       </c>
       <c r="BI5" t="n">
-        <v>11750000</v>
+        <v>33454000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-484000</v>
+        <v>-254000</v>
       </c>
       <c r="BK5" t="n">
-        <v>12234000</v>
+        <v>33708000</v>
       </c>
       <c r="BL5" t="n">
-        <v>17339000</v>
+        <v>22040000</v>
       </c>
       <c r="BM5" t="n">
-        <v>17339000</v>
+        <v>22040000</v>
       </c>
       <c r="BN5" t="n">
-        <v>17339000</v>
+        <v>22040000</v>
       </c>
     </row>
   </sheetData>
@@ -2482,516 +2482,516 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45535</v>
+        <v>44439</v>
       </c>
       <c r="B2" t="n">
-        <v>-3144000</v>
+        <v>31905000</v>
       </c>
       <c r="C2" t="n">
-        <v>-2750000</v>
+        <v>-19335000</v>
       </c>
       <c r="D2" t="n">
-        <v>9355000</v>
+        <v>7353000</v>
       </c>
       <c r="E2" t="n">
-        <v>-14240000</v>
+        <v>-6611000</v>
       </c>
       <c r="F2" t="n">
-        <v>22040000</v>
+        <v>17339000</v>
       </c>
       <c r="G2" t="n">
-        <v>26787000</v>
+        <v>14975000</v>
       </c>
       <c r="H2" t="n">
-        <v>-421000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-4326000</v>
+        <v>2364000</v>
       </c>
       <c r="J2" t="n">
-        <v>1312000</v>
+        <v>-15593000</v>
       </c>
       <c r="K2" t="n">
-        <v>-3870000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-3870000</v>
-      </c>
+        <v>-2554000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>6605000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6605000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-2750000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>9355000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+        <v>-11982000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>-11982000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-19335000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7353000</v>
+      </c>
       <c r="T2" t="n">
-        <v>-16734000</v>
+        <v>-20559000</v>
       </c>
       <c r="U2" t="n">
-        <v>-2494000</v>
+        <v>-13948000</v>
       </c>
       <c r="V2" t="n">
-        <v>-2494000</v>
+        <v>-13948000</v>
       </c>
       <c r="W2" t="n">
-        <v>-3040000</v>
+        <v>-591000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3040000</v>
+        <v>-591000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1540000</v>
+        <v>-1126000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1540000</v>
+        <v>-1126000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-9660000</v>
+        <v>-4894000</v>
       </c>
       <c r="AC2" t="n">
-        <v>11096000</v>
+        <v>38516000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1781000</v>
+        <v>-9741000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2403000</v>
+        <v>-311000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-8914000</v>
+        <v>1737000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-10367000</v>
+        <v>-773000</v>
       </c>
       <c r="AH2" t="n">
-        <v>6362000</v>
+        <v>-1023000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-4909000</v>
+        <v>3533000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2326000</v>
+        <v>403000</v>
       </c>
       <c r="AK2" t="n">
-        <v>158000</v>
+        <v>973000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-104000</v>
+        <v>6759000</v>
       </c>
       <c r="AM2" t="n">
-        <v>14085000</v>
+        <v>10148000</v>
       </c>
       <c r="AN2" t="n">
-        <v>11198000</v>
+        <v>8126000</v>
       </c>
       <c r="AO2" t="n">
-        <v>2887000</v>
+        <v>2022000</v>
       </c>
       <c r="AP2" t="n">
-        <v>241000</v>
+        <v>333000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>88000</v>
+        <v>502000</v>
       </c>
       <c r="AR2" t="n">
-        <v>2608000</v>
+        <v>28279000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45169</v>
+        <v>44804</v>
       </c>
       <c r="B3" t="n">
-        <v>11941000</v>
+        <v>-4045000</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>15226000</v>
+        <v>13228000</v>
       </c>
       <c r="E3" t="n">
-        <v>-14391000</v>
+        <v>-12508000</v>
       </c>
       <c r="F3" t="n">
-        <v>26787000</v>
+        <v>12758000</v>
       </c>
       <c r="G3" t="n">
-        <v>12758000</v>
+        <v>17339000</v>
       </c>
       <c r="H3" t="n">
-        <v>-954000</v>
+        <v>731000</v>
       </c>
       <c r="I3" t="n">
-        <v>14983000</v>
+        <v>-5312000</v>
       </c>
       <c r="J3" t="n">
-        <v>10190000</v>
+        <v>8826000</v>
       </c>
       <c r="K3" t="n">
-        <v>-3609000</v>
+        <v>-3234000</v>
       </c>
       <c r="L3" t="n">
-        <v>-3609000</v>
+        <v>-3234000</v>
       </c>
       <c r="M3" t="n">
-        <v>15226000</v>
+        <v>13228000</v>
       </c>
       <c r="N3" t="n">
-        <v>15226000</v>
-      </c>
-      <c r="O3" t="n">
+        <v>13228000</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>13228000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>13228000</v>
+      </c>
+      <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
-        <v>15226000</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>13228000</v>
+      </c>
       <c r="T3" t="n">
-        <v>-21539000</v>
+        <v>-22601000</v>
       </c>
       <c r="U3" t="n">
-        <v>-7153000</v>
+        <v>-10923000</v>
       </c>
       <c r="V3" t="n">
-        <v>-7153000</v>
+        <v>-10923000</v>
       </c>
       <c r="W3" t="n">
-        <v>-2019000</v>
+        <v>-2265000</v>
       </c>
       <c r="X3" t="n">
-        <v>5000</v>
+        <v>830000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2024000</v>
+        <v>-3095000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3204000</v>
+        <v>-1045000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3204000</v>
+        <v>-1045000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-9163000</v>
+        <v>-8368000</v>
       </c>
       <c r="AC3" t="n">
-        <v>26332000</v>
+        <v>8463000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1856000</v>
+        <v>-3380000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1699000</v>
+        <v>-330000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-7593000</v>
+        <v>-26919000</v>
       </c>
       <c r="AG3" t="n">
-        <v>2922000</v>
+        <v>12988000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-6916000</v>
+        <v>-27591000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-3599000</v>
+        <v>-12316000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1697000</v>
+        <v>107000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-246000</v>
+        <v>1313000</v>
       </c>
       <c r="AL3" t="n">
-        <v>4951000</v>
+        <v>5773000</v>
       </c>
       <c r="AM3" t="n">
-        <v>12538000</v>
+        <v>12106000</v>
       </c>
       <c r="AN3" t="n">
-        <v>9861000</v>
+        <v>9883000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2677000</v>
+        <v>2223000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-331000</v>
+        <v>-2364000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>214000</v>
+        <v>-701000</v>
       </c>
       <c r="AR3" t="n">
-        <v>17797000</v>
+        <v>24776000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44804</v>
+        <v>45169</v>
       </c>
       <c r="B4" t="n">
-        <v>-4045000</v>
+        <v>11941000</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>13228000</v>
+        <v>15226000</v>
       </c>
       <c r="E4" t="n">
-        <v>-12508000</v>
+        <v>-14391000</v>
       </c>
       <c r="F4" t="n">
+        <v>26787000</v>
+      </c>
+      <c r="G4" t="n">
         <v>12758000</v>
       </c>
-      <c r="G4" t="n">
-        <v>17339000</v>
-      </c>
       <c r="H4" t="n">
-        <v>731000</v>
+        <v>-954000</v>
       </c>
       <c r="I4" t="n">
-        <v>-5312000</v>
+        <v>14983000</v>
       </c>
       <c r="J4" t="n">
-        <v>8826000</v>
+        <v>10190000</v>
       </c>
       <c r="K4" t="n">
-        <v>-3234000</v>
+        <v>-3609000</v>
       </c>
       <c r="L4" t="n">
-        <v>-3234000</v>
+        <v>-3609000</v>
       </c>
       <c r="M4" t="n">
-        <v>13228000</v>
+        <v>15226000</v>
       </c>
       <c r="N4" t="n">
-        <v>13228000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>15226000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>13228000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>13228000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>13228000</v>
-      </c>
+        <v>15226000</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>-22601000</v>
+        <v>-21539000</v>
       </c>
       <c r="U4" t="n">
-        <v>-10923000</v>
+        <v>-7153000</v>
       </c>
       <c r="V4" t="n">
-        <v>-10923000</v>
+        <v>-7153000</v>
       </c>
       <c r="W4" t="n">
-        <v>-2265000</v>
+        <v>-2019000</v>
       </c>
       <c r="X4" t="n">
-        <v>830000</v>
+        <v>5000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-3095000</v>
+        <v>-2024000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1045000</v>
+        <v>-3204000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1045000</v>
+        <v>-3204000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-8368000</v>
+        <v>-9163000</v>
       </c>
       <c r="AC4" t="n">
-        <v>8463000</v>
+        <v>26332000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3380000</v>
+        <v>-1856000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-330000</v>
+        <v>-1699000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-26919000</v>
+        <v>-7593000</v>
       </c>
       <c r="AG4" t="n">
-        <v>12988000</v>
+        <v>2922000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-27591000</v>
+        <v>-6916000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-12316000</v>
+        <v>-3599000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>107000</v>
+        <v>1697000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1313000</v>
+        <v>-246000</v>
       </c>
       <c r="AL4" t="n">
-        <v>5773000</v>
+        <v>4951000</v>
       </c>
       <c r="AM4" t="n">
-        <v>12106000</v>
+        <v>12538000</v>
       </c>
       <c r="AN4" t="n">
-        <v>9883000</v>
+        <v>9861000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2223000</v>
+        <v>2677000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2364000</v>
+        <v>-331000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-701000</v>
+        <v>214000</v>
       </c>
       <c r="AR4" t="n">
-        <v>24776000</v>
+        <v>17797000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44439</v>
+        <v>45535</v>
       </c>
       <c r="B5" t="n">
-        <v>31905000</v>
+        <v>-3144000</v>
       </c>
       <c r="C5" t="n">
-        <v>-19335000</v>
+        <v>-2750000</v>
       </c>
       <c r="D5" t="n">
-        <v>7353000</v>
+        <v>9355000</v>
       </c>
       <c r="E5" t="n">
-        <v>-6611000</v>
+        <v>-14240000</v>
       </c>
       <c r="F5" t="n">
-        <v>17339000</v>
+        <v>22040000</v>
       </c>
       <c r="G5" t="n">
-        <v>14975000</v>
+        <v>26787000</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-421000</v>
       </c>
       <c r="I5" t="n">
-        <v>2364000</v>
+        <v>-4326000</v>
       </c>
       <c r="J5" t="n">
-        <v>-15593000</v>
+        <v>1312000</v>
       </c>
       <c r="K5" t="n">
-        <v>-2554000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>-3870000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-3870000</v>
+      </c>
       <c r="M5" t="n">
-        <v>-11982000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>-11982000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-19335000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>7353000</v>
-      </c>
+        <v>6605000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6605000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-2750000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>9355000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-20559000</v>
+        <v>-16734000</v>
       </c>
       <c r="U5" t="n">
-        <v>-13948000</v>
+        <v>-2494000</v>
       </c>
       <c r="V5" t="n">
-        <v>-13948000</v>
+        <v>-2494000</v>
       </c>
       <c r="W5" t="n">
-        <v>-591000</v>
+        <v>-3040000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-591000</v>
+        <v>-3040000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1126000</v>
+        <v>-1540000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1126000</v>
+        <v>-1540000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-4894000</v>
+        <v>-9660000</v>
       </c>
       <c r="AC5" t="n">
-        <v>38516000</v>
+        <v>11096000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-9741000</v>
+        <v>-1781000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-311000</v>
+        <v>-2403000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1737000</v>
+        <v>-8914000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-773000</v>
+        <v>-10367000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1023000</v>
+        <v>6362000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3533000</v>
+        <v>-4909000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>403000</v>
+        <v>2326000</v>
       </c>
       <c r="AK5" t="n">
-        <v>973000</v>
+        <v>158000</v>
       </c>
       <c r="AL5" t="n">
-        <v>6759000</v>
+        <v>-104000</v>
       </c>
       <c r="AM5" t="n">
-        <v>10148000</v>
+        <v>14085000</v>
       </c>
       <c r="AN5" t="n">
-        <v>8126000</v>
+        <v>11198000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2022000</v>
+        <v>2887000</v>
       </c>
       <c r="AP5" t="n">
-        <v>333000</v>
+        <v>241000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>502000</v>
+        <v>88000</v>
       </c>
       <c r="AR5" t="n">
-        <v>28279000</v>
+        <v>2608000</v>
       </c>
     </row>
   </sheetData>
@@ -3571,197 +3571,197 @@
       </c>
       <c r="DI1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EV1" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Philip Stephen Dudderidge O.B.E.', 'age': 76, 'title': 'Founder &amp; Non-Executive Chairman', 'yearBorn': 1949, 'fiscalYear': 2024, 'totalPay': 233252, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Timothy Paul Carroll', 'age': 63, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 527704, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sally Ann Mckone', 'age': 57, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1968, 'fiscalYear': 2024, 'totalPay': 413387, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Timothy  Dingley', 'age': 44, 'title': 'Chief Operations Officer', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Simon  Bannister', 'title': 'Chief Information Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Francine  Godrich', 'title': 'Group General Counsel &amp; Company Secretary', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Alicia  Cousins', 'title': 'Chief People Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Damian  Hawley', 'age': 54, 'title': 'Chief Revenue Officer', 'yearBorn': 1971, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Andy  Land', 'title': 'Head of Sustainability', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Christian  Hellinger', 'title': 'Chief Executive Officer of ADAM Audio', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Philip Stephen Dudderidge O.B.E.', 'age': 76, 'title': 'Founder &amp; Non-Executive Chairman', 'yearBorn': 1949, 'fiscalYear': 2024, 'totalPay': 232740, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Timothy Paul Carroll', 'age': 63, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 526544, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Sally Ann Mckone', 'age': 57, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1968, 'fiscalYear': 2024, 'totalPay': 412479, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Timothy  Dingley', 'age': 44, 'title': 'Chief Operations Officer', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Simon  Bannister', 'title': 'Chief Information Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Francine  Godrich', 'title': 'Group General Counsel &amp; Company Secretary', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Alicia  Cousins', 'title': 'Chief People Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Damian  Hawley', 'age': 54, 'title': 'Chief Revenue Officer', 'yearBorn': 1971, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Andy  Land', 'title': 'Head of Sustainability', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Christian  Hellinger', 'title': 'Chief Executive Officer of ADAM Audio', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3867,7 +3867,7 @@
         <v>6</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1735603200</v>
@@ -3884,34 +3884,34 @@
         <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AI2" t="n">
         <v>0.05</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AK2" t="n">
         <v>1764201600</v>
@@ -3923,10 +3923,10 @@
         <v>1.74</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.091</v>
+        <v>1.085</v>
       </c>
       <c r="AO2" t="n">
-        <v>21.400002</v>
+        <v>21.800001</v>
       </c>
       <c r="AP2" t="n">
         <v>4</v>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AW2" t="n">
-        <v>124273168</v>
+        <v>126596032</v>
       </c>
       <c r="AX2" t="n">
-        <v>132100253</v>
+        <v>135485653</v>
       </c>
       <c r="AY2" t="n">
         <v>1.66</v>
@@ -3968,19 +3968,19 @@
         <v>1.52</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.73572296</v>
+        <v>0.7494748</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.9884</v>
+        <v>2.0712</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.23225</v>
+        <v>2.25375</v>
       </c>
       <c r="BF2" t="n">
         <v>0.042</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.020000001</v>
+        <v>0.019444443</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>135118160</v>
+        <v>137441024</v>
       </c>
       <c r="BK2" t="n">
         <v>0.03178</v>
@@ -4006,16 +4006,16 @@
         <v>0.42124</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.51251</v>
+        <v>0.51313</v>
       </c>
       <c r="BP2" t="n">
         <v>58071572</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.3452227</v>
+        <v>2.340069</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.91249335</v>
+        <v>0.93159646</v>
       </c>
       <c r="BS2" t="n">
         <v>1756598400</v>
@@ -4036,16 +4036,16 @@
         <v>0.1</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.8</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="BZ2" t="n">
-        <v>5.856</v>
+        <v>5.957</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.14130437</v>
+        <v>0.11917102</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="CC2" t="n">
         <v>0.021</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
@@ -4161,146 +4161,146 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1602136800000</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.925925</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DM2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DJ2" t="n">
-        <v>1780380366</v>
-      </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DN2" t="n">
+        <v>1782108773</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>finmb_278290596</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="inlineStr">
         <is>
           <t>Focusrite PLC                 R</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>Focusrite plc</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>PREPRE</t>
         </is>
       </c>
-      <c r="DN2" t="n">
-        <v>0.0400002</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>2.14 - 2.14</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DY2" t="n">
+        <v>0.01999998</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>2.18 - 2.18</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
         <is>
           <t>Frankfurt</t>
         </is>
       </c>
-      <c r="DQ2" t="n">
+      <c r="EB2" t="n">
         <v>12</v>
       </c>
-      <c r="DR2" t="n">
-        <v>0.48000014</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.2891567</v>
-      </c>
-      <c r="DT2" t="inlineStr">
+      <c r="EC2" t="n">
+        <v>0.5200001</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.31325307</v>
+      </c>
+      <c r="EE2" t="inlineStr">
         <is>
           <t>1.66 - 2.8</t>
         </is>
       </c>
-      <c r="DU2" t="n">
-        <v>-0.6599998500000001</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.23571424</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>14.130438</v>
-      </c>
-      <c r="DX2" t="n">
+      <c r="EF2" t="n">
+        <v>-0.6199999</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.22142853</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>11.917103</v>
+      </c>
+      <c r="EI2" t="n">
         <v>1745906406</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="EJ2" t="n">
         <v>1745906406</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EK2" t="n">
         <v>1746007200</v>
       </c>
-      <c r="EA2" t="n">
+      <c r="EL2" t="n">
         <v>1746007200</v>
       </c>
-      <c r="EB2" t="b">
+      <c r="EM2" t="b">
         <v>0</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EN2" t="n">
         <v>0.1</v>
       </c>
-      <c r="ED2" t="n">
-        <v>0.15160012</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.07624227</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.09224987</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.04132596</v>
-      </c>
-      <c r="EH2" t="n">
+      <c r="EO2" t="n">
+        <v>0.10880017</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>0.05253002</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-0.07375002</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-0.032723248</v>
+      </c>
+      <c r="ES2" t="n">
         <v>15</v>
       </c>
-      <c r="EI2" t="n">
+      <c r="ET2" t="n">
         <v>15</v>
       </c>
-      <c r="EJ2" t="b">
+      <c r="EU2" t="b">
         <v>0</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1602136800000</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>finmb_278290596</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="EQ2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="ES2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>1.9047714</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>2.14</v>
       </c>
       <c r="EV2" t="inlineStr"/>
     </row>
